--- a/data/Data_for_figures_4results/Result4_HubScore_Synergy and Tradeoff.xlsx
+++ b/data/Data_for_figures_4results/Result4_HubScore_Synergy and Tradeoff.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\City SDG paper\data for governance capacity\WGI_data_072026\1_Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\State_SDG\Github\SDG_Interactions-driven-by-Urban_Typologies\data\Data_for_figures_4results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BB6960-1483-4605-885E-A450A6EF12AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE0F3580-0610-48E6-98DB-50C01898E0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11256" yWindow="2304" windowWidth="12060" windowHeight="11316" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="204" yWindow="768" windowWidth="24372" windowHeight="9024" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,10 +447,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>0.86254332540969003</v>
+        <v>0.86207391785778398</v>
       </c>
       <c r="D2">
-        <v>0.38207995878725598</v>
+        <v>0.374827677118581</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -461,10 +461,10 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>0.69168494824928195</v>
+        <v>0.69292304123307402</v>
       </c>
       <c r="D3">
-        <v>0.52344196380723396</v>
+        <v>0.50548833038977603</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -475,10 +475,10 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>0.91619860391011898</v>
+        <v>0.91601895535123701</v>
       </c>
       <c r="D4">
-        <v>0.459079683908452</v>
+        <v>0.48007053290289398</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -489,10 +489,10 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>0.46131453988105797</v>
+        <v>0.461315272574993</v>
       </c>
       <c r="D5">
-        <v>0.23828898752445099</v>
+        <v>0.24061898632776199</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -503,10 +503,10 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>7.5386202259451904E-2</v>
+        <v>4.6681913891370497E-2</v>
       </c>
       <c r="D6">
-        <v>0.77969653532836403</v>
+        <v>0.57014238123845895</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -517,10 +517,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>9.7298810166853503E-2</v>
+        <v>9.7418795212865603E-2</v>
       </c>
       <c r="D7">
-        <v>0.23366119635839799</v>
+        <v>0.20921716621405501</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -531,10 +531,10 @@
         <v>11</v>
       </c>
       <c r="C8">
-        <v>9.6692219704781701E-2</v>
+        <v>9.7097155781328298E-2</v>
       </c>
       <c r="D8">
-        <v>0.25170142327301298</v>
+        <v>0.196436075178472</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -545,10 +545,10 @@
         <v>12</v>
       </c>
       <c r="C9">
-        <v>0.58339351847455201</v>
+        <v>0.58332954795103698</v>
       </c>
       <c r="D9">
-        <v>0.246737348161122</v>
+        <v>0.244351151510104</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -562,7 +562,7 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0.136575173563349</v>
+        <v>0.15201218751419501</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -573,10 +573,10 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>0.32954441281917002</v>
+        <v>0.31119011219543102</v>
       </c>
       <c r="D11">
-        <v>0.460355708999586</v>
+        <v>0.50750080061884395</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -587,7 +587,7 @@
         <v>15</v>
       </c>
       <c r="C12">
-        <v>0.43452815973992598</v>
+        <v>0.433253421008647</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -601,10 +601,10 @@
         <v>16</v>
       </c>
       <c r="C13">
-        <v>5.7617770416629799E-2</v>
+        <v>5.9148383590064198E-2</v>
       </c>
       <c r="D13">
-        <v>0.75701968833176503</v>
+        <v>0.74407399821289399</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -615,10 +615,10 @@
         <v>17</v>
       </c>
       <c r="C14">
-        <v>0.53832847014531104</v>
+        <v>0.54007832889505902</v>
       </c>
       <c r="D14">
-        <v>0.49465263108437602</v>
+        <v>0.45415339649772302</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -629,10 +629,10 @@
         <v>18</v>
       </c>
       <c r="C15">
-        <v>0.27949230302713102</v>
+        <v>0.27991940797527398</v>
       </c>
       <c r="D15">
-        <v>0.10820162960436699</v>
+        <v>9.3023699396022203E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -643,10 +643,10 @@
         <v>19</v>
       </c>
       <c r="C16">
-        <v>0.83690073027628697</v>
+        <v>0.837502278433646</v>
       </c>
       <c r="D16">
-        <v>0.274940350481305</v>
+        <v>0.29741807186211799</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -657,10 +657,10 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>0.72889084433331797</v>
+        <v>0.72977311514509902</v>
       </c>
       <c r="D17">
-        <v>2.1357786268952701E-2</v>
+        <v>2.6012886634628099E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -671,10 +671,10 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>0.62650469362962102</v>
+        <v>0.63206292088882299</v>
       </c>
       <c r="D18">
-        <v>4.0432682292094103E-2</v>
+        <v>3.9826070973796798E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -685,10 +685,10 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>0.92136066773814895</v>
+        <v>0.91808841284431397</v>
       </c>
       <c r="D19">
-        <v>0.122470999603064</v>
+        <v>0.13141339667665999</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -699,10 +699,10 @@
         <v>8</v>
       </c>
       <c r="C20">
-        <v>0.33121550358601798</v>
+        <v>0.33314928371415298</v>
       </c>
       <c r="D20">
-        <v>0.236030937625413</v>
+        <v>0.26698254473789101</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -713,10 +713,10 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>6.1189357195618098E-2</v>
+        <v>3.4830003741892497E-2</v>
       </c>
       <c r="D21">
-        <v>0.195842766419214</v>
+        <v>0.31245671600084601</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -727,10 +727,10 @@
         <v>10</v>
       </c>
       <c r="C22">
-        <v>0.124682912191714</v>
+        <v>0.1244837476327</v>
       </c>
       <c r="D22">
-        <v>5.3698895424902401E-2</v>
+        <v>6.26808995333306E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -741,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="C23">
-        <v>0.12774863704228601</v>
+        <v>0.12565440131848701</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -755,10 +755,10 @@
         <v>12</v>
       </c>
       <c r="C24">
-        <v>0.56175730866864904</v>
+        <v>0.56677939877601902</v>
       </c>
       <c r="D24">
-        <v>4.5674778000789201E-2</v>
+        <v>4.9585121540754798E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -772,7 +772,7 @@
         <v>1</v>
       </c>
       <c r="D25">
-        <v>3.7351031327582503E-2</v>
+        <v>3.9937994533814802E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -783,10 +783,10 @@
         <v>14</v>
       </c>
       <c r="C26">
-        <v>0.29347634668607703</v>
+        <v>0.30109538979527201</v>
       </c>
       <c r="D26">
-        <v>0.20960820708728001</v>
+        <v>0.20128242009642699</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -797,10 +797,10 @@
         <v>15</v>
       </c>
       <c r="C27">
-        <v>0.360964023042188</v>
+        <v>0.35738143396067401</v>
       </c>
       <c r="D27">
-        <v>0.23835258503201301</v>
+        <v>0.265102920037048</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -811,10 +811,10 @@
         <v>16</v>
       </c>
       <c r="C28">
-        <v>7.2660789448718899E-2</v>
+        <v>7.2250052845815996E-2</v>
       </c>
       <c r="D28">
-        <v>8.3604394783626995E-2</v>
+        <v>9.0324829538572002E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -825,10 +825,10 @@
         <v>17</v>
       </c>
       <c r="C29">
-        <v>0.35092642394170498</v>
+        <v>0.34625300579162399</v>
       </c>
       <c r="D29">
-        <v>4.1041745814994299E-2</v>
+        <v>5.3989869851932701E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -839,10 +839,10 @@
         <v>18</v>
       </c>
       <c r="C30">
-        <v>0.26052542539622803</v>
+        <v>0.26024951032076798</v>
       </c>
       <c r="D30">
-        <v>1.4204872982461401E-2</v>
+        <v>1.3080162933601199E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -853,10 +853,10 @@
         <v>19</v>
       </c>
       <c r="C31">
-        <v>0.415416438833978</v>
+        <v>0.41377777696783302</v>
       </c>
       <c r="D31">
-        <v>0.15455927100507</v>
+        <v>0.19741787031942201</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -867,10 +867,10 @@
         <v>5</v>
       </c>
       <c r="C32">
-        <v>0.40422629109951902</v>
+        <v>0.40734917322434799</v>
       </c>
       <c r="D32">
-        <v>0.57700360551345498</v>
+        <v>0.53492715248692702</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -881,10 +881,10 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.21083899122904901</v>
+        <v>0.21600941590661199</v>
       </c>
       <c r="D33">
-        <v>0.21480164463291501</v>
+        <v>0.155962450161791</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -895,10 +895,10 @@
         <v>7</v>
       </c>
       <c r="C34">
-        <v>0.18679465546815599</v>
+        <v>0.189229139086697</v>
       </c>
       <c r="D34">
-        <v>0.38181935709982701</v>
+        <v>0.39935726272230898</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -909,10 +909,10 @@
         <v>8</v>
       </c>
       <c r="C35">
-        <v>0.24897513036813701</v>
+        <v>0.25800397033803701</v>
       </c>
       <c r="D35">
-        <v>0.24918651764090799</v>
+        <v>0.16276849739344901</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -923,10 +923,10 @@
         <v>9</v>
       </c>
       <c r="C36">
-        <v>2.57140562555042E-2</v>
+        <v>6.409326537144E-2</v>
       </c>
       <c r="D36">
-        <v>0.45635648691094999</v>
+        <v>0.32905661267423297</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -937,10 +937,10 @@
         <v>10</v>
       </c>
       <c r="C37">
-        <v>8.1221103501971703E-2</v>
+        <v>8.3495979942792994E-2</v>
       </c>
       <c r="D37">
-        <v>0.12596337479557601</v>
+        <v>0.12610344725627801</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -951,10 +951,10 @@
         <v>11</v>
       </c>
       <c r="C38">
-        <v>8.6404454588882407E-2</v>
+        <v>9.3924361557526606E-2</v>
       </c>
       <c r="D38">
-        <v>5.9527399117463103E-2</v>
+        <v>3.4004453330246501E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -965,10 +965,10 @@
         <v>12</v>
       </c>
       <c r="C39">
-        <v>0.35666280707764703</v>
+        <v>0.36201924370284999</v>
       </c>
       <c r="D39">
-        <v>0.568360813089821</v>
+        <v>0.56871653383663601</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="D40">
-        <v>0.27905462381406798</v>
+        <v>0.30542211210780501</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -993,10 +993,10 @@
         <v>14</v>
       </c>
       <c r="C41">
-        <v>0.200117890775728</v>
+        <v>0.15070329411813699</v>
       </c>
       <c r="D41">
-        <v>0.13805803168008701</v>
+        <v>0.18443214932038801</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1007,10 +1007,10 @@
         <v>15</v>
       </c>
       <c r="C42">
-        <v>0.29007624149553601</v>
+        <v>0.29132841268188497</v>
       </c>
       <c r="D42">
-        <v>6.6248069365030804E-2</v>
+        <v>6.4743949025742306E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1021,7 +1021,7 @@
         <v>16</v>
       </c>
       <c r="C43">
-        <v>1.0292580578686801E-2</v>
+        <v>1.2123281713723E-2</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1035,10 +1035,10 @@
         <v>17</v>
       </c>
       <c r="C44">
-        <v>0.22724601182692999</v>
+        <v>0.229453931834535</v>
       </c>
       <c r="D44">
-        <v>0.147867706449546</v>
+        <v>7.7705057500810096E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1049,10 +1049,10 @@
         <v>18</v>
       </c>
       <c r="C45">
-        <v>2.5096114644422102E-2</v>
+        <v>2.57072224012126E-2</v>
       </c>
       <c r="D45">
-        <v>0.484564391863684</v>
+        <v>0.47528780500279499</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1063,10 +1063,10 @@
         <v>19</v>
       </c>
       <c r="C46">
-        <v>6.9605888473494498E-2</v>
+        <v>7.1808479524906405E-2</v>
       </c>
       <c r="D46">
-        <v>0.18820820354318701</v>
+        <v>0.18199208130571201</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1077,10 +1077,10 @@
         <v>5</v>
       </c>
       <c r="C47">
-        <v>0.33460410925022799</v>
+        <v>0.34241097031259699</v>
       </c>
       <c r="D47">
-        <v>0.441505268789879</v>
+        <v>0.49450880199734998</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1091,10 +1091,10 @@
         <v>6</v>
       </c>
       <c r="C48">
-        <v>0.26388390041069698</v>
+        <v>0.29328332696760701</v>
       </c>
       <c r="D48">
-        <v>0.61044682456116695</v>
+        <v>0.58289857664233802</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1105,10 +1105,10 @@
         <v>7</v>
       </c>
       <c r="C49">
-        <v>0.523803199458165</v>
+        <v>0.55113478847081199</v>
       </c>
       <c r="D49">
-        <v>0.39996179284850197</v>
+        <v>0.36819630793872998</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1119,10 +1119,10 @@
         <v>8</v>
       </c>
       <c r="C50">
-        <v>0.25790606207758698</v>
+        <v>0.25457146949165799</v>
       </c>
       <c r="D50">
-        <v>0.35681666891462799</v>
+        <v>0.41903296120515598</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -1133,10 +1133,10 @@
         <v>9</v>
       </c>
       <c r="C51">
-        <v>0.25031946567220398</v>
+        <v>0.36580244755198399</v>
       </c>
       <c r="D51">
-        <v>0.76119316725150299</v>
+        <v>0.31036918149947101</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -1147,10 +1147,10 @@
         <v>10</v>
       </c>
       <c r="C52">
-        <v>7.4507484639754304E-2</v>
+        <v>7.4798542848624999E-2</v>
       </c>
       <c r="D52">
-        <v>0.88860554357060795</v>
+        <v>0.94837901154145099</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1161,10 +1161,10 @@
         <v>11</v>
       </c>
       <c r="C53">
-        <v>0.175025556008225</v>
+        <v>0.20448815800741499</v>
       </c>
       <c r="D53">
-        <v>0.126676144817746</v>
+        <v>7.8075940035068001E-2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -1175,10 +1175,10 @@
         <v>12</v>
       </c>
       <c r="C54">
-        <v>0.33383527454877199</v>
+        <v>0.33106733098099</v>
       </c>
       <c r="D54">
-        <v>0.34028086944187702</v>
+        <v>0.40164825828124201</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1192,7 +1192,7 @@
         <v>1</v>
       </c>
       <c r="D55">
-        <v>0.102708617565424</v>
+        <v>0.114067968018892</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1203,10 +1203,10 @@
         <v>14</v>
       </c>
       <c r="C56">
-        <v>0.20139008636389799</v>
+        <v>0.20944043736470799</v>
       </c>
       <c r="D56">
-        <v>0.35822779157412199</v>
+        <v>0.39558316983472602</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -1217,7 +1217,7 @@
         <v>15</v>
       </c>
       <c r="C57">
-        <v>0.24078437832244701</v>
+        <v>0.24911734533451901</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -1231,10 +1231,10 @@
         <v>16</v>
       </c>
       <c r="C58">
-        <v>5.9234725994359798E-2</v>
+        <v>5.9047263664542798E-2</v>
       </c>
       <c r="D58">
-        <v>0.21790064840304699</v>
+        <v>0.20133991964925499</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -1245,10 +1245,10 @@
         <v>17</v>
       </c>
       <c r="C59">
-        <v>0.28351098399986602</v>
+        <v>0.30753156655237002</v>
       </c>
       <c r="D59">
-        <v>0.32836258335452201</v>
+        <v>0.266517276419868</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -1259,10 +1259,10 @@
         <v>18</v>
       </c>
       <c r="C60">
-        <v>0.172346923920106</v>
+        <v>0.20855378666664601</v>
       </c>
       <c r="D60">
-        <v>0.166838511733085</v>
+        <v>3.1169786848183199E-2</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -1273,10 +1273,10 @@
         <v>19</v>
       </c>
       <c r="C61">
-        <v>0.20234588836171899</v>
+        <v>0.205264830331082</v>
       </c>
       <c r="D61">
-        <v>4.8606263141846802E-2</v>
+        <v>5.5394030812326099E-2</v>
       </c>
     </row>
   </sheetData>
